--- a/_to_delete/1-2_5370648400813399211_domrf_partial.xlsx
+++ b/_to_delete/1-2_5370648400813399211_domrf_partial.xlsx
@@ -261,737 +261,737 @@
   <commentList>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф; пример пользователя подтверждает номер ПД.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Номер ПД из индексированной страницы проверки дом.рф; адрес взят из исходной строки как fallback.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированных сниппетов дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E6" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированных сниппетов дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E7" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E8" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/27247</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E10" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E11" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E13" authorId="0" shapeId="0">
       <text>
-        <t>Из индексированного сниппета карточки дом.рф.</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E14" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/31074</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E15" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/32274</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E16" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/32319</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E17" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/37984</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/39716</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/39827</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E20" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/40634</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/42848</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E22" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/42849</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E23" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/43199</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/44125</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E25" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/44476</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E26" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/44596</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E27" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45091</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E28" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45092</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E29" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45093</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45094</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45184</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E32" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45185</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45519</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E34" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45826</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E35" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46127</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46163</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E37" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46278</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E38" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46281</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E39" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46310</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E40" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46644</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E41" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46646</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46647</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E43" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46648</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E44" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/46687</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/47431</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/47508</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E47" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/47510</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/47511</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E49" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/48353</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/48767</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/48805</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E52" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/49356</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E53" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/49357</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E54" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/49777</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E55" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50144</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50237</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E57" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50238</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E58" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50291</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50407</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E60" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50408</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E61" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50409</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50420</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E63" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50448</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E64" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50975</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E65" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50976</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51108</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E67" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51119</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51437</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E69" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51438</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51439</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51440</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E72" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51725</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51928</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E74" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/52082</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/52381</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E76" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/52453</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E77" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/52454</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/52790</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E79" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53150</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E80" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53411</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53412</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E82" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53413</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53498</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E84" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53519</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E85" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53520</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E86" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53521</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E87" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53522</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E88" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53523</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E89" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53542</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E90" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53543</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E91" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53581</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E92" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/53669</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E93" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54505</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E94" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54521</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E95" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54541</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E96" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54578</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E97" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54579</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E98" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54580</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E99" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54581</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E100" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54582</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E101" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54583</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E102" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54897</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E103" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/55224</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E104" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/55472</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E105" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/55760</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E106" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56071</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E107" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56102</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E108" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56157</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E109" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56224</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E110" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56304</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E111" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56305</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E112" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56306</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E113" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56307</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E114" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56514</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E115" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/45970</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E116" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56715</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E117" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56866</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E118" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56944</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E119" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56945</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E120" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56949</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E121" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/56950</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E122" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/57478</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E123" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/58298</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E124" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/58299</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E125" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/58524</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E126" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/59897</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E127" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/60712</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E128" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/61221</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E129" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/50365</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E130" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/51432</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E131" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/54528</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E132" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/55103</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E133" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/57291</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E134" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/57465</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E135" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/57807</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E136" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/58300</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E137" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/58488</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E138" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/58489</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E139" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/60425</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E140" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/62125</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E141" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/62998</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E142" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/63646</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E143" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/65505</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E144" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/66242</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E145" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/67699</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E146" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/67700</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E147" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/69273</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
     <comment ref="E148" authorId="0" shapeId="0">
       <text>
-        <t>https://???.???.??/???????/???????-??????????/??????/70718</t>
+        <t>Source: nash.dom.rf object card visible page text.</t>
       </text>
     </comment>
   </commentList>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E1" s="22" t="inlineStr">
         <is>
-          <t>Источник/статус</t>
+          <t>Источник</t>
         </is>
       </c>
       <c r="F1" s="22" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C3" s="36" t="inlineStr">
         <is>
-          <t>ГОРОД МОСКВА, район Муниципальный округ Пресненский, наб Краснопресненская, д. 14А, корпус 1</t>
+          <t>Москва город, ГОРОД МОСКВА, район Муниципальный округ Пресненский, наб Краснопресненская, д. 14А, корпус 1</t>
         </is>
       </c>
       <c r="D3" s="36" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>ГОРОД МОСКВА, Район Внуково, д. 11, корпус 3</t>
+          <t>Москва город, ГОРОД МОСКВА, Район Внуково</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>г. Москва, ул Илимская, корпус 7, вл. 3/5</t>
+          <t>Москва город, ГОРОД МОСКВА, Район Люблино</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
@@ -1961,12 +1961,24 @@
           <t>27247</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Жилой комплекс"Люблинский парк"</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Люблино</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>77-001669</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/27247</t>
         </is>
       </c>
       <c r="F8" s="26" t="inlineStr">
@@ -2567,12 +2579,24 @@
           <t>31074</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>ТИТУЛ Империал</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Таганский район</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>77-001842</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/31074</t>
         </is>
       </c>
       <c r="F14" s="26" t="inlineStr">
@@ -2658,12 +2682,24 @@
           <t>32274</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>Файв Тауэрс</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Донской район</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>77-001871</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/32274</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
@@ -2748,12 +2784,24 @@
           <t>32319</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>ЖК STELLAR CITY</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Можайский район</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>77-001869</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/32319</t>
         </is>
       </c>
       <c r="F16" s="26" t="inlineStr">
@@ -2838,12 +2886,24 @@
           <t>37984</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Бадаевский</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Дорогомилово</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>77-002139</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/37984</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
@@ -2929,12 +2989,24 @@
           <t>39716</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Русские Сезоны</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Замоскворечье</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>77-002215</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/39716</t>
         </is>
       </c>
       <c r="F18" s="26" t="inlineStr">
@@ -3020,12 +3092,24 @@
           <t>39827</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Инноватор"</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Раменки</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="inlineStr">
+        <is>
+          <t>77-002230</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/39827</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
@@ -3110,12 +3194,24 @@
           <t>40634</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>77-002246</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/40634</t>
         </is>
       </c>
       <c r="F20" s="26" t="inlineStr">
@@ -3203,12 +3299,24 @@
           <t>42848</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Жилой комплекс Воксхолл</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Замоскворечье</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>77-002323</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/42848</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
@@ -3293,12 +3401,24 @@
           <t>42849</t>
         </is>
       </c>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Жилой комплекс Воксхолл</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Замоскворечье</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>77-002324</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/42849</t>
         </is>
       </c>
       <c r="F22" s="26" t="inlineStr">
@@ -3383,12 +3503,24 @@
           <t>43199</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "ЛЕГАСИ"</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Раменки</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>77-002336</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/43199</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
@@ -3474,12 +3606,24 @@
           <t>44125</t>
         </is>
       </c>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>ЖК "Интеллигент"</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Басманный район</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>77-002363</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/44125</t>
         </is>
       </c>
       <c r="F24" s="26" t="inlineStr">
@@ -3564,12 +3708,24 @@
           <t>44476</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Фон Дессин</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Басманный район</t>
+        </is>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>77-002380</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/44476</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
@@ -3654,12 +3810,24 @@
           <t>44596</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Шелепиха</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Пресненский район</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>77-002383</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/44596</t>
         </is>
       </c>
       <c r="F26" s="26" t="inlineStr">
@@ -3745,12 +3913,24 @@
           <t>45091</t>
         </is>
       </c>
-      <c r="B27" s="36" t="n"/>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="36" t="n"/>
-      <c r="E27" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>Жилой квартал "Цветочные Поляны Экопарк"</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D27" s="36" t="inlineStr">
+        <is>
+          <t>77-002419</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45091</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
@@ -3836,12 +4016,24 @@
           <t>45092</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Жилой квартал "Цветочные Поляны Экопарк"</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>77-002419</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45092</t>
         </is>
       </c>
       <c r="F28" s="26" t="inlineStr">
@@ -3927,12 +4119,24 @@
           <t>45093</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n"/>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>Жилой квартал "Цветочные Поляны Экопарк"</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>77-002419</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45093</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
@@ -4018,12 +4222,24 @@
           <t>45094</t>
         </is>
       </c>
-      <c r="B30" s="27" t="n"/>
-      <c r="C30" s="27" t="n"/>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Жилой квартал "Цветочные Поляны Экопарк"</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>77-002419</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45094</t>
         </is>
       </c>
       <c r="F30" s="26" t="inlineStr">
@@ -4109,12 +4325,24 @@
           <t>45184</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n"/>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B31" s="36" t="inlineStr">
+        <is>
+          <t>Верейская 41</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Можайский район</t>
+        </is>
+      </c>
+      <c r="D31" s="36" t="inlineStr">
+        <is>
+          <t>77-002429</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45184</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
@@ -4199,12 +4427,24 @@
           <t>45185</t>
         </is>
       </c>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>Верейская 41</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Можайский район</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>77-002429</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45185</t>
         </is>
       </c>
       <c r="F32" s="26" t="inlineStr">
@@ -4289,12 +4529,24 @@
           <t>45519</t>
         </is>
       </c>
-      <c r="B33" s="36" t="n"/>
-      <c r="C33" s="36" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>Левел Южнопортовая</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Печатники</t>
+        </is>
+      </c>
+      <c r="D33" s="36" t="inlineStr">
+        <is>
+          <t>77-002461</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45519</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
@@ -4379,12 +4631,24 @@
           <t>45826</t>
         </is>
       </c>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Нагатино Ай-Лэнд</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Даниловский район</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>77-002467</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45826</t>
         </is>
       </c>
       <c r="F34" s="26" t="inlineStr">
@@ -4470,12 +4734,24 @@
           <t>46127</t>
         </is>
       </c>
-      <c r="B35" s="36" t="n"/>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>ФСК Sydney City</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Хорошёво-Мнёвники</t>
+        </is>
+      </c>
+      <c r="D35" s="36" t="inlineStr">
+        <is>
+          <t>77-002502</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46127</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
@@ -4561,12 +4837,24 @@
           <t>46163</t>
         </is>
       </c>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="27" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>ЖК "Первый Нагатинский"</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Нагатино-Садовники</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>77-002507</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46163</t>
         </is>
       </c>
       <c r="F36" s="26" t="inlineStr">
@@ -4652,12 +4940,24 @@
           <t>46278</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n"/>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B37" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В11 СберСити</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Кунцево</t>
+        </is>
+      </c>
+      <c r="D37" s="36" t="inlineStr">
+        <is>
+          <t>77-002515</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46278</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
@@ -4743,12 +5043,24 @@
           <t>46281</t>
         </is>
       </c>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="27" t="n"/>
-      <c r="D38" s="27" t="n"/>
-      <c r="E38" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В12 СберСити</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Кунцево</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>77-002516</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46281</t>
         </is>
       </c>
       <c r="F38" s="26" t="inlineStr">
@@ -4834,12 +5146,24 @@
           <t>46310</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n"/>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B39" s="36" t="inlineStr">
+        <is>
+          <t>Life Time</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Пресненский район</t>
+        </is>
+      </c>
+      <c r="D39" s="36" t="inlineStr">
+        <is>
+          <t>77-002520</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46310</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
@@ -4925,12 +5249,24 @@
           <t>46644</t>
         </is>
       </c>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="27" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В19 корпус 1 СберСити</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>77-002571</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46644</t>
         </is>
       </c>
       <c r="F40" s="26" t="inlineStr">
@@ -5016,12 +5352,24 @@
           <t>46646</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n"/>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="36" t="n"/>
-      <c r="E41" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B41" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В19 корпус 2 СберСити</t>
+        </is>
+      </c>
+      <c r="C41" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D41" s="36" t="inlineStr">
+        <is>
+          <t>77-002571</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46646</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
@@ -5107,12 +5455,24 @@
           <t>46647</t>
         </is>
       </c>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="27" t="n"/>
-      <c r="D42" s="27" t="n"/>
-      <c r="E42" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В20 корпус 1 СберСити</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="inlineStr">
+        <is>
+          <t>77-002574</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46647</t>
         </is>
       </c>
       <c r="F42" s="26" t="inlineStr">
@@ -5198,12 +5558,24 @@
           <t>46648</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B43" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В20 корпус 2 СберСити</t>
+        </is>
+      </c>
+      <c r="C43" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D43" s="36" t="inlineStr">
+        <is>
+          <t>77-002574</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46648</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
@@ -5289,12 +5661,24 @@
           <t>46687</t>
         </is>
       </c>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Жилой комплекс Репаблик</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Пресненский район</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>77-002583</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/46687</t>
         </is>
       </c>
       <c r="F44" s="26" t="inlineStr">
@@ -5380,12 +5764,24 @@
           <t>47431</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n"/>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B45" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Бадаевский</t>
+        </is>
+      </c>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Дорогомилово</t>
+        </is>
+      </c>
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>77-002680</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/47431</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
@@ -5471,12 +5867,24 @@
           <t>47508</t>
         </is>
       </c>
-      <c r="B46" s="27" t="n"/>
-      <c r="C46" s="27" t="n"/>
-      <c r="D46" s="27" t="n"/>
-      <c r="E46" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Жилой комплекс Внуково Кантри Клаб</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Первомайское</t>
+        </is>
+      </c>
+      <c r="D46" s="27" t="inlineStr">
+        <is>
+          <t>77-002700</t>
+        </is>
+      </c>
+      <c r="E46" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/47508</t>
         </is>
       </c>
       <c r="F46" s="26" t="inlineStr">
@@ -5561,12 +5969,24 @@
           <t>47510</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n"/>
-      <c r="C47" s="36" t="n"/>
-      <c r="D47" s="36" t="n"/>
-      <c r="E47" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B47" s="36" t="inlineStr">
+        <is>
+          <t>Жилой комплекс Внуково Кантри Клаб</t>
+        </is>
+      </c>
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Первомайское</t>
+        </is>
+      </c>
+      <c r="D47" s="36" t="inlineStr">
+        <is>
+          <t>77-002700</t>
+        </is>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/47510</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
@@ -5651,12 +6071,24 @@
           <t>47511</t>
         </is>
       </c>
-      <c r="B48" s="27" t="n"/>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-      <c r="E48" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Жилой комплекс Внуково Кантри Клаб</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Первомайское</t>
+        </is>
+      </c>
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>77-002700</t>
+        </is>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/47511</t>
         </is>
       </c>
       <c r="F48" s="26" t="inlineStr">
@@ -5742,12 +6174,24 @@
           <t>48353</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n"/>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B49" s="36" t="inlineStr">
+        <is>
+          <t>АННАБЕЛЬ</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Муниципальный округ Хамовники, пер Курсовой, д. 12/5, строение 7</t>
+        </is>
+      </c>
+      <c r="D49" s="36" t="inlineStr">
+        <is>
+          <t>77-002758</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/48353</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
@@ -5832,12 +6276,24 @@
           <t>48767</t>
         </is>
       </c>
-      <c r="B50" s="27" t="n"/>
-      <c r="C50" s="27" t="n"/>
-      <c r="D50" s="27" t="n"/>
-      <c r="E50" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>МФК Коллекция Лужники (жилые корпуса)</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Хамовники</t>
+        </is>
+      </c>
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>77-002773</t>
+        </is>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/48767</t>
         </is>
       </c>
       <c r="F50" s="26" t="inlineStr">
@@ -5922,12 +6378,24 @@
           <t>48805</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n"/>
-      <c r="C51" s="36" t="n"/>
-      <c r="D51" s="36" t="n"/>
-      <c r="E51" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B51" s="36" t="inlineStr">
+        <is>
+          <t>Лё Дом / Le Dome</t>
+        </is>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Хамовники</t>
+        </is>
+      </c>
+      <c r="D51" s="36" t="inlineStr">
+        <is>
+          <t>77-002775</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/48805</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
@@ -6013,12 +6481,24 @@
           <t>49356</t>
         </is>
       </c>
-      <c r="B52" s="27" t="n"/>
-      <c r="C52" s="27" t="n"/>
-      <c r="D52" s="27" t="n"/>
-      <c r="E52" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>Русич Кантемировский</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Царицыно</t>
+        </is>
+      </c>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>77-002782</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/49356</t>
         </is>
       </c>
       <c r="F52" s="26" t="inlineStr">
@@ -6104,12 +6584,24 @@
           <t>49357</t>
         </is>
       </c>
-      <c r="B53" s="36" t="n"/>
-      <c r="C53" s="36" t="n"/>
-      <c r="D53" s="36" t="n"/>
-      <c r="E53" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B53" s="36" t="inlineStr">
+        <is>
+          <t>Русич Кантемировский</t>
+        </is>
+      </c>
+      <c r="C53" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Царицыно</t>
+        </is>
+      </c>
+      <c r="D53" s="36" t="inlineStr">
+        <is>
+          <t>77-002782</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/49357</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
@@ -6195,12 +6687,24 @@
           <t>49777</t>
         </is>
       </c>
-      <c r="B54" s="27" t="n"/>
-      <c r="C54" s="27" t="n"/>
-      <c r="D54" s="27" t="n"/>
-      <c r="E54" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>Нагатино Ай-Лэнд</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Даниловский район</t>
+        </is>
+      </c>
+      <c r="D54" s="27" t="inlineStr">
+        <is>
+          <t>77-002800</t>
+        </is>
+      </c>
+      <c r="E54" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/49777</t>
         </is>
       </c>
       <c r="F54" s="26" t="inlineStr">
@@ -6286,12 +6790,24 @@
           <t>50144</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n"/>
-      <c r="C55" s="36" t="n"/>
-      <c r="D55" s="36" t="n"/>
-      <c r="E55" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B55" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Страна.Озёрная</t>
+        </is>
+      </c>
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Муниципальный округ Очаково-Матвеевское, д. 1, корпус 2</t>
+        </is>
+      </c>
+      <c r="D55" s="36" t="inlineStr">
+        <is>
+          <t>77-002808</t>
+        </is>
+      </c>
+      <c r="E55" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50144</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
@@ -6377,12 +6893,24 @@
           <t>50237</t>
         </is>
       </c>
-      <c r="B56" s="27" t="n"/>
-      <c r="C56" s="27" t="n"/>
-      <c r="D56" s="27" t="n"/>
-      <c r="E56" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>ЖК "Новое Внуково"</t>
+        </is>
+      </c>
+      <c r="C56" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Внуково</t>
+        </is>
+      </c>
+      <c r="D56" s="27" t="inlineStr">
+        <is>
+          <t>77-002815</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50237</t>
         </is>
       </c>
       <c r="F56" s="26" t="inlineStr">
@@ -6468,12 +6996,24 @@
           <t>50238</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n"/>
-      <c r="C57" s="36" t="n"/>
-      <c r="D57" s="36" t="n"/>
-      <c r="E57" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B57" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Новое Внуково"</t>
+        </is>
+      </c>
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Внуково</t>
+        </is>
+      </c>
+      <c r="D57" s="36" t="inlineStr">
+        <is>
+          <t>77-002815</t>
+        </is>
+      </c>
+      <c r="E57" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50238</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
@@ -6558,12 +7098,24 @@
           <t>50291</t>
         </is>
       </c>
-      <c r="B58" s="27" t="n"/>
-      <c r="C58" s="27" t="n"/>
-      <c r="D58" s="27" t="n"/>
-      <c r="E58" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>БРЮСОВ</t>
+        </is>
+      </c>
+      <c r="C58" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Пресненский район</t>
+        </is>
+      </c>
+      <c r="D58" s="27" t="inlineStr">
+        <is>
+          <t>77-002818</t>
+        </is>
+      </c>
+      <c r="E58" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50291</t>
         </is>
       </c>
       <c r="F58" s="26" t="inlineStr">
@@ -6649,12 +7201,24 @@
           <t>50407</t>
         </is>
       </c>
-      <c r="B59" s="36" t="n"/>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="36" t="n"/>
-      <c r="E59" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B59" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В21 корпус 1 СберСити</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D59" s="36" t="inlineStr">
+        <is>
+          <t>77-002821</t>
+        </is>
+      </c>
+      <c r="E59" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50407</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
@@ -6739,12 +7303,24 @@
           <t>50408</t>
         </is>
       </c>
-      <c r="B60" s="27" t="n"/>
-      <c r="C60" s="27" t="n"/>
-      <c r="D60" s="27" t="n"/>
-      <c r="E60" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В21 корпус 2 СберСити</t>
+        </is>
+      </c>
+      <c r="C60" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D60" s="27" t="inlineStr">
+        <is>
+          <t>77-002821</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50408</t>
         </is>
       </c>
       <c r="F60" s="26" t="inlineStr">
@@ -6829,12 +7405,24 @@
           <t>50409</t>
         </is>
       </c>
-      <c r="B61" s="36" t="n"/>
-      <c r="C61" s="36" t="n"/>
-      <c r="D61" s="36" t="n"/>
-      <c r="E61" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B61" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В21 корпус 3 СберСити</t>
+        </is>
+      </c>
+      <c r="C61" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D61" s="36" t="inlineStr">
+        <is>
+          <t>77-002821</t>
+        </is>
+      </c>
+      <c r="E61" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50409</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
@@ -6919,12 +7507,24 @@
           <t>50420</t>
         </is>
       </c>
-      <c r="B62" s="27" t="n"/>
-      <c r="C62" s="27" t="n"/>
-      <c r="D62" s="27" t="n"/>
-      <c r="E62" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>Жилой Комплекс "Цветочные Поляны Сити"</t>
+        </is>
+      </c>
+      <c r="C62" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Филимонковское</t>
+        </is>
+      </c>
+      <c r="D62" s="27" t="inlineStr">
+        <is>
+          <t>77-002823</t>
+        </is>
+      </c>
+      <c r="E62" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50420</t>
         </is>
       </c>
       <c r="F62" s="26" t="inlineStr">
@@ -7010,12 +7610,24 @@
           <t>50448</t>
         </is>
       </c>
-      <c r="B63" s="36" t="n"/>
-      <c r="C63" s="36" t="n"/>
-      <c r="D63" s="36" t="n"/>
-      <c r="E63" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B63" s="36" t="inlineStr">
+        <is>
+          <t>Жилой комплекс "Цветочные Поляны Сити"</t>
+        </is>
+      </c>
+      <c r="C63" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D63" s="36" t="inlineStr">
+        <is>
+          <t>77-002825</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50448</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
@@ -7101,12 +7713,24 @@
           <t>50975</t>
         </is>
       </c>
-      <c r="B64" s="27" t="n"/>
-      <c r="C64" s="27" t="n"/>
-      <c r="D64" s="27" t="n"/>
-      <c r="E64" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>Квартал Марьино</t>
+        </is>
+      </c>
+      <c r="C64" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Филимонковское</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>77-002832</t>
+        </is>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50975</t>
         </is>
       </c>
       <c r="F64" s="26" t="inlineStr">
@@ -7192,12 +7816,24 @@
           <t>50976</t>
         </is>
       </c>
-      <c r="B65" s="36" t="n"/>
-      <c r="C65" s="36" t="n"/>
-      <c r="D65" s="36" t="n"/>
-      <c r="E65" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B65" s="36" t="inlineStr">
+        <is>
+          <t>Квартал Марьино</t>
+        </is>
+      </c>
+      <c r="C65" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Филимонковское</t>
+        </is>
+      </c>
+      <c r="D65" s="36" t="inlineStr">
+        <is>
+          <t>77-002832</t>
+        </is>
+      </c>
+      <c r="E65" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50976</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
@@ -7283,12 +7919,24 @@
           <t>51108</t>
         </is>
       </c>
-      <c r="B66" s="27" t="n"/>
-      <c r="C66" s="27" t="n"/>
-      <c r="D66" s="27" t="n"/>
-      <c r="E66" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>Жилой Комплекс "Цветочные Поляны Сити"</t>
+        </is>
+      </c>
+      <c r="C66" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D66" s="27" t="inlineStr">
+        <is>
+          <t>77-002835</t>
+        </is>
+      </c>
+      <c r="E66" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51108</t>
         </is>
       </c>
       <c r="F66" s="26" t="inlineStr">
@@ -7374,12 +8022,24 @@
           <t>51119</t>
         </is>
       </c>
-      <c r="B67" s="36" t="n"/>
-      <c r="C67" s="36" t="n"/>
-      <c r="D67" s="36" t="n"/>
-      <c r="E67" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B67" s="36" t="inlineStr">
+        <is>
+          <t>Жилой Комплекс "Цветочные Поляны Сити"</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D67" s="36" t="inlineStr">
+        <is>
+          <t>77-002836</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51119</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
@@ -7465,12 +8125,24 @@
           <t>51437</t>
         </is>
       </c>
-      <c r="B68" s="27" t="n"/>
-      <c r="C68" s="27" t="n"/>
-      <c r="D68" s="27" t="n"/>
-      <c r="E68" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>Подольские кварталы</t>
+        </is>
+      </c>
+      <c r="C68" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Щербинка</t>
+        </is>
+      </c>
+      <c r="D68" s="27" t="inlineStr">
+        <is>
+          <t>77-002846</t>
+        </is>
+      </c>
+      <c r="E68" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51437</t>
         </is>
       </c>
       <c r="F68" s="26" t="inlineStr">
@@ -7556,12 +8228,24 @@
           <t>51438</t>
         </is>
       </c>
-      <c r="B69" s="36" t="n"/>
-      <c r="C69" s="36" t="n"/>
-      <c r="D69" s="36" t="n"/>
-      <c r="E69" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B69" s="36" t="inlineStr">
+        <is>
+          <t>Подольские кварталы</t>
+        </is>
+      </c>
+      <c r="C69" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Щербинка</t>
+        </is>
+      </c>
+      <c r="D69" s="36" t="inlineStr">
+        <is>
+          <t>77-002846</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51438</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
@@ -7647,12 +8331,24 @@
           <t>51439</t>
         </is>
       </c>
-      <c r="B70" s="27" t="n"/>
-      <c r="C70" s="27" t="n"/>
-      <c r="D70" s="27" t="n"/>
-      <c r="E70" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B70" s="27" t="inlineStr">
+        <is>
+          <t>Подольские кварталы</t>
+        </is>
+      </c>
+      <c r="C70" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Щербинка</t>
+        </is>
+      </c>
+      <c r="D70" s="27" t="inlineStr">
+        <is>
+          <t>77-002846</t>
+        </is>
+      </c>
+      <c r="E70" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51439</t>
         </is>
       </c>
       <c r="F70" s="26" t="inlineStr">
@@ -7738,12 +8434,24 @@
           <t>51440</t>
         </is>
       </c>
-      <c r="B71" s="36" t="n"/>
-      <c r="C71" s="36" t="n"/>
-      <c r="D71" s="36" t="n"/>
-      <c r="E71" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>Подольские кварталы</t>
+        </is>
+      </c>
+      <c r="C71" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Щербинка</t>
+        </is>
+      </c>
+      <c r="D71" s="36" t="inlineStr">
+        <is>
+          <t>77-002846</t>
+        </is>
+      </c>
+      <c r="E71" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51440</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
@@ -7829,12 +8537,24 @@
           <t>51725</t>
         </is>
       </c>
-      <c r="B72" s="27" t="n"/>
-      <c r="C72" s="27" t="n"/>
-      <c r="D72" s="27" t="n"/>
-      <c r="E72" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>"Кристалл"</t>
+        </is>
+      </c>
+      <c r="C72" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Хорошёво-Мнёвники</t>
+        </is>
+      </c>
+      <c r="D72" s="27" t="inlineStr">
+        <is>
+          <t>77-002852</t>
+        </is>
+      </c>
+      <c r="E72" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51725</t>
         </is>
       </c>
       <c r="F72" s="26" t="inlineStr">
@@ -7920,12 +8640,24 @@
           <t>51928</t>
         </is>
       </c>
-      <c r="B73" s="36" t="n"/>
-      <c r="C73" s="36" t="n"/>
-      <c r="D73" s="36" t="n"/>
-      <c r="E73" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B73" s="36" t="inlineStr">
+        <is>
+          <t>Сити Бэй</t>
+        </is>
+      </c>
+      <c r="C73" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Покровское-Стрешнево</t>
+        </is>
+      </c>
+      <c r="D73" s="36" t="inlineStr">
+        <is>
+          <t>77-002854</t>
+        </is>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51928</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
@@ -8011,12 +8743,24 @@
           <t>52082</t>
         </is>
       </c>
-      <c r="B74" s="27" t="n"/>
-      <c r="C74" s="27" t="n"/>
-      <c r="D74" s="27" t="n"/>
-      <c r="E74" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>ФСК Sydney City</t>
+        </is>
+      </c>
+      <c r="C74" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Хорошёво-Мнёвники</t>
+        </is>
+      </c>
+      <c r="D74" s="27" t="inlineStr">
+        <is>
+          <t>77-002862</t>
+        </is>
+      </c>
+      <c r="E74" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/52082</t>
         </is>
       </c>
       <c r="F74" s="26" t="inlineStr">
@@ -8103,12 +8847,24 @@
           <t>52381</t>
         </is>
       </c>
-      <c r="B75" s="36" t="n"/>
-      <c r="C75" s="36" t="n"/>
-      <c r="D75" s="36" t="n"/>
-      <c r="E75" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B75" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Дом на Зорге"</t>
+        </is>
+      </c>
+      <c r="C75" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Сокол</t>
+        </is>
+      </c>
+      <c r="D75" s="36" t="inlineStr">
+        <is>
+          <t>77-002871</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/52381</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
@@ -8193,12 +8949,24 @@
           <t>52453</t>
         </is>
       </c>
-      <c r="B76" s="27" t="n"/>
-      <c r="C76" s="27" t="n"/>
-      <c r="D76" s="27" t="n"/>
-      <c r="E76" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>СОЮЗ</t>
+        </is>
+      </c>
+      <c r="C76" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, ул Сельскохозяйственная</t>
+        </is>
+      </c>
+      <c r="D76" s="27" t="inlineStr">
+        <is>
+          <t>77-002873</t>
+        </is>
+      </c>
+      <c r="E76" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/52453</t>
         </is>
       </c>
       <c r="F76" s="26" t="inlineStr">
@@ -8284,12 +9052,24 @@
           <t>52454</t>
         </is>
       </c>
-      <c r="B77" s="36" t="n"/>
-      <c r="C77" s="36" t="n"/>
-      <c r="D77" s="36" t="n"/>
-      <c r="E77" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B77" s="36" t="inlineStr">
+        <is>
+          <t>СОЮЗ</t>
+        </is>
+      </c>
+      <c r="C77" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, ул Сельскохозяйственная</t>
+        </is>
+      </c>
+      <c r="D77" s="36" t="inlineStr">
+        <is>
+          <t>77-002873</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/52454</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
@@ -8375,12 +9155,24 @@
           <t>52790</t>
         </is>
       </c>
-      <c r="B78" s="27" t="n"/>
-      <c r="C78" s="27" t="n"/>
-      <c r="D78" s="27" t="n"/>
-      <c r="E78" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>Жилой дом "Высотка на Жукова"</t>
+        </is>
+      </c>
+      <c r="C78" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Хорошёво-Мнёвники</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>77-002877</t>
+        </is>
+      </c>
+      <c r="E78" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/52790</t>
         </is>
       </c>
       <c r="F78" s="26" t="inlineStr">
@@ -8466,12 +9258,24 @@
           <t>53150</t>
         </is>
       </c>
-      <c r="B79" s="36" t="n"/>
-      <c r="C79" s="36" t="n"/>
-      <c r="D79" s="36" t="n"/>
-      <c r="E79" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B79" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Дзен-кварталы"</t>
+        </is>
+      </c>
+      <c r="C79" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Коммунарка</t>
+        </is>
+      </c>
+      <c r="D79" s="36" t="inlineStr">
+        <is>
+          <t>77-002883</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53150</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
@@ -8556,12 +9360,24 @@
           <t>53411</t>
         </is>
       </c>
-      <c r="B80" s="27" t="n"/>
-      <c r="C80" s="27" t="n"/>
-      <c r="D80" s="27" t="n"/>
-      <c r="E80" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>ЖК "Новое Внуково"</t>
+        </is>
+      </c>
+      <c r="C80" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Внуково</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>77-002885</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53411</t>
         </is>
       </c>
       <c r="F80" s="26" t="inlineStr">
@@ -8647,12 +9463,24 @@
           <t>53412</t>
         </is>
       </c>
-      <c r="B81" s="36" t="n"/>
-      <c r="C81" s="36" t="n"/>
-      <c r="D81" s="36" t="n"/>
-      <c r="E81" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B81" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Новое Внуково"</t>
+        </is>
+      </c>
+      <c r="C81" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Внуково</t>
+        </is>
+      </c>
+      <c r="D81" s="36" t="inlineStr">
+        <is>
+          <t>77-002885</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53412</t>
         </is>
       </c>
       <c r="F81" s="35" t="inlineStr">
@@ -8738,12 +9566,24 @@
           <t>53413</t>
         </is>
       </c>
-      <c r="B82" s="27" t="n"/>
-      <c r="C82" s="27" t="n"/>
-      <c r="D82" s="27" t="n"/>
-      <c r="E82" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>ЖК "Новое Внуково"</t>
+        </is>
+      </c>
+      <c r="C82" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Внуково</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>77-002885</t>
+        </is>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53413</t>
         </is>
       </c>
       <c r="F82" s="26" t="inlineStr">
@@ -8829,12 +9669,24 @@
           <t>53498</t>
         </is>
       </c>
-      <c r="B83" s="36" t="n"/>
-      <c r="C83" s="36" t="n"/>
-      <c r="D83" s="36" t="n"/>
-      <c r="E83" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Скандинавия"</t>
+        </is>
+      </c>
+      <c r="C83" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Коммунарка</t>
+        </is>
+      </c>
+      <c r="D83" s="36" t="inlineStr">
+        <is>
+          <t>77-002889</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53498</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
@@ -8920,12 +9772,24 @@
           <t>53519</t>
         </is>
       </c>
-      <c r="B84" s="27" t="n"/>
-      <c r="C84" s="27" t="n"/>
-      <c r="D84" s="27" t="n"/>
-      <c r="E84" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В14 корпус 1 СберСити</t>
+        </is>
+      </c>
+      <c r="C84" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>77-002891</t>
+        </is>
+      </c>
+      <c r="E84" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53519</t>
         </is>
       </c>
       <c r="F84" s="26" t="inlineStr">
@@ -9010,12 +9874,24 @@
           <t>53520</t>
         </is>
       </c>
-      <c r="B85" s="36" t="n"/>
-      <c r="C85" s="36" t="n"/>
-      <c r="D85" s="36" t="n"/>
-      <c r="E85" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B85" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В14 корпус 2 СберСити</t>
+        </is>
+      </c>
+      <c r="C85" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D85" s="36" t="inlineStr">
+        <is>
+          <t>77-002891</t>
+        </is>
+      </c>
+      <c r="E85" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53520</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
@@ -9100,12 +9976,24 @@
           <t>53521</t>
         </is>
       </c>
-      <c r="B86" s="27" t="n"/>
-      <c r="C86" s="27" t="n"/>
-      <c r="D86" s="27" t="n"/>
-      <c r="E86" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В14 корпус 3 СберСити</t>
+        </is>
+      </c>
+      <c r="C86" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>77-002891</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53521</t>
         </is>
       </c>
       <c r="F86" s="26" t="inlineStr">
@@ -9190,12 +10078,24 @@
           <t>53522</t>
         </is>
       </c>
-      <c r="B87" s="36" t="n"/>
-      <c r="C87" s="36" t="n"/>
-      <c r="D87" s="36" t="n"/>
-      <c r="E87" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B87" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В14 корпус 4 СберСити</t>
+        </is>
+      </c>
+      <c r="C87" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D87" s="36" t="inlineStr">
+        <is>
+          <t>77-002891</t>
+        </is>
+      </c>
+      <c r="E87" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53522</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
@@ -9280,12 +10180,24 @@
           <t>53523</t>
         </is>
       </c>
-      <c r="B88" s="27" t="n"/>
-      <c r="C88" s="27" t="n"/>
-      <c r="D88" s="27" t="n"/>
-      <c r="E88" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В14 корпус 5 СберСити</t>
+        </is>
+      </c>
+      <c r="C88" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>77-002891</t>
+        </is>
+      </c>
+      <c r="E88" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53523</t>
         </is>
       </c>
       <c r="F88" s="26" t="inlineStr">
@@ -9370,12 +10282,24 @@
           <t>53542</t>
         </is>
       </c>
-      <c r="B89" s="36" t="n"/>
-      <c r="C89" s="36" t="n"/>
-      <c r="D89" s="36" t="n"/>
-      <c r="E89" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B89" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Ольховый Квартал</t>
+        </is>
+      </c>
+      <c r="C89" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Коммунарка</t>
+        </is>
+      </c>
+      <c r="D89" s="36" t="inlineStr">
+        <is>
+          <t>77-002893</t>
+        </is>
+      </c>
+      <c r="E89" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53542</t>
         </is>
       </c>
       <c r="F89" s="35" t="inlineStr">
@@ -9461,12 +10385,24 @@
           <t>53543</t>
         </is>
       </c>
-      <c r="B90" s="27" t="n"/>
-      <c r="C90" s="27" t="n"/>
-      <c r="D90" s="27" t="n"/>
-      <c r="E90" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Ольховый Квартал</t>
+        </is>
+      </c>
+      <c r="C90" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Коммунарка</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>77-002893</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53543</t>
         </is>
       </c>
       <c r="F90" s="26" t="inlineStr">
@@ -9552,12 +10488,24 @@
           <t>53581</t>
         </is>
       </c>
-      <c r="B91" s="36" t="n"/>
-      <c r="C91" s="36" t="n"/>
-      <c r="D91" s="36" t="n"/>
-      <c r="E91" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B91" s="36" t="inlineStr">
+        <is>
+          <t>Квартал Домашний,ЖК Квартал Домашний</t>
+        </is>
+      </c>
+      <c r="C91" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Марьино</t>
+        </is>
+      </c>
+      <c r="D91" s="36" t="inlineStr">
+        <is>
+          <t>77-002895</t>
+        </is>
+      </c>
+      <c r="E91" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53581</t>
         </is>
       </c>
       <c r="F91" s="35" t="inlineStr">
@@ -9642,12 +10590,24 @@
           <t>53669</t>
         </is>
       </c>
-      <c r="B92" s="27" t="n"/>
-      <c r="C92" s="27" t="n"/>
-      <c r="D92" s="27" t="n"/>
-      <c r="E92" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>LUCE / ЛЮЧЕ</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Муниципальный округ Арбат, пер Крестовоздвиженский, д. 4</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>77-002903</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/53669</t>
         </is>
       </c>
       <c r="F92" s="26" t="inlineStr">
@@ -9733,12 +10693,24 @@
           <t>54505</t>
         </is>
       </c>
-      <c r="B93" s="36" t="n"/>
-      <c r="C93" s="36" t="n"/>
-      <c r="D93" s="36" t="n"/>
-      <c r="E93" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B93" s="36" t="inlineStr">
+        <is>
+          <t>Молжаниново, ЖК Молжаниново</t>
+        </is>
+      </c>
+      <c r="C93" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Молжаниновский район</t>
+        </is>
+      </c>
+      <c r="D93" s="36" t="inlineStr">
+        <is>
+          <t>77-002926</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54505</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
@@ -9824,12 +10796,24 @@
           <t>54521</t>
         </is>
       </c>
-      <c r="B94" s="27" t="n"/>
-      <c r="C94" s="27" t="n"/>
-      <c r="D94" s="27" t="n"/>
-      <c r="E94" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>Жилой Комплекс "Холланд парк"</t>
+        </is>
+      </c>
+      <c r="C94" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Покровское-Стрешнево</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>77-002927</t>
+        </is>
+      </c>
+      <c r="E94" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54521</t>
         </is>
       </c>
       <c r="F94" s="26" t="inlineStr">
@@ -9914,12 +10898,24 @@
           <t>54541</t>
         </is>
       </c>
-      <c r="B95" s="36" t="n"/>
-      <c r="C95" s="36" t="n"/>
-      <c r="D95" s="36" t="n"/>
-      <c r="E95" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B95" s="36" t="inlineStr">
+        <is>
+          <t>Молжаниново, ЖК Молжаниново</t>
+        </is>
+      </c>
+      <c r="C95" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Молжаниновский район</t>
+        </is>
+      </c>
+      <c r="D95" s="36" t="inlineStr">
+        <is>
+          <t>77-002929</t>
+        </is>
+      </c>
+      <c r="E95" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54541</t>
         </is>
       </c>
       <c r="F95" s="35" t="inlineStr">
@@ -10005,12 +11001,24 @@
           <t>54578</t>
         </is>
       </c>
-      <c r="B96" s="27" t="n"/>
-      <c r="C96" s="27" t="n"/>
-      <c r="D96" s="27" t="n"/>
-      <c r="E96" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В17 корпус 1 СберСити</t>
+        </is>
+      </c>
+      <c r="C96" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, район р-н Кунцево</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>77-002931</t>
+        </is>
+      </c>
+      <c r="E96" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54578</t>
         </is>
       </c>
       <c r="F96" s="26" t="inlineStr">
@@ -10096,12 +11104,24 @@
           <t>54579</t>
         </is>
       </c>
-      <c r="B97" s="36" t="n"/>
-      <c r="C97" s="36" t="n"/>
-      <c r="D97" s="36" t="n"/>
-      <c r="E97" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B97" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В17 корпус 2 СберСити</t>
+        </is>
+      </c>
+      <c r="C97" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, район Р-н Кунцево</t>
+        </is>
+      </c>
+      <c r="D97" s="36" t="inlineStr">
+        <is>
+          <t>77-002931</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54579</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
@@ -10187,12 +11207,24 @@
           <t>54580</t>
         </is>
       </c>
-      <c r="B98" s="27" t="n"/>
-      <c r="C98" s="27" t="n"/>
-      <c r="D98" s="27" t="n"/>
-      <c r="E98" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B98" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В17 корпус 3 СберСити</t>
+        </is>
+      </c>
+      <c r="C98" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, район р-н Кунцево</t>
+        </is>
+      </c>
+      <c r="D98" s="27" t="inlineStr">
+        <is>
+          <t>77-002931</t>
+        </is>
+      </c>
+      <c r="E98" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54580</t>
         </is>
       </c>
       <c r="F98" s="26" t="inlineStr">
@@ -10278,12 +11310,24 @@
           <t>54581</t>
         </is>
       </c>
-      <c r="B99" s="36" t="n"/>
-      <c r="C99" s="36" t="n"/>
-      <c r="D99" s="36" t="n"/>
-      <c r="E99" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B99" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В17 корпус 4 СберСити</t>
+        </is>
+      </c>
+      <c r="C99" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, район р-н Кунцево</t>
+        </is>
+      </c>
+      <c r="D99" s="36" t="inlineStr">
+        <is>
+          <t>77-002931</t>
+        </is>
+      </c>
+      <c r="E99" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54581</t>
         </is>
       </c>
       <c r="F99" s="35" t="inlineStr">
@@ -10369,12 +11413,24 @@
           <t>54582</t>
         </is>
       </c>
-      <c r="B100" s="27" t="n"/>
-      <c r="C100" s="27" t="n"/>
-      <c r="D100" s="27" t="n"/>
-      <c r="E100" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>Квартал В17 корпус 5 СберСити</t>
+        </is>
+      </c>
+      <c r="C100" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, район р-н Кунцево</t>
+        </is>
+      </c>
+      <c r="D100" s="27" t="inlineStr">
+        <is>
+          <t>77-002931</t>
+        </is>
+      </c>
+      <c r="E100" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54582</t>
         </is>
       </c>
       <c r="F100" s="26" t="inlineStr">
@@ -10460,12 +11516,24 @@
           <t>54583</t>
         </is>
       </c>
-      <c r="B101" s="36" t="n"/>
-      <c r="C101" s="36" t="n"/>
-      <c r="D101" s="36" t="n"/>
-      <c r="E101" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B101" s="36" t="inlineStr">
+        <is>
+          <t>Квартал В17 корпус 6 СберСити</t>
+        </is>
+      </c>
+      <c r="C101" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, район р-н Кунцево</t>
+        </is>
+      </c>
+      <c r="D101" s="36" t="inlineStr">
+        <is>
+          <t>77-002931</t>
+        </is>
+      </c>
+      <c r="E101" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54583</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
@@ -10551,12 +11619,24 @@
           <t>54897</t>
         </is>
       </c>
-      <c r="B102" s="27" t="n"/>
-      <c r="C102" s="27" t="n"/>
-      <c r="D102" s="27" t="n"/>
-      <c r="E102" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>Скандинавия</t>
+        </is>
+      </c>
+      <c r="C102" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Сосенское</t>
+        </is>
+      </c>
+      <c r="D102" s="27" t="inlineStr">
+        <is>
+          <t>77-002937</t>
+        </is>
+      </c>
+      <c r="E102" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54897</t>
         </is>
       </c>
       <c r="F102" s="26" t="inlineStr">
@@ -10641,12 +11721,24 @@
           <t>55224</t>
         </is>
       </c>
-      <c r="B103" s="36" t="n"/>
-      <c r="C103" s="36" t="n"/>
-      <c r="D103" s="36" t="n"/>
-      <c r="E103" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B103" s="36" t="inlineStr">
+        <is>
+          <t>Бунинские кварталы</t>
+        </is>
+      </c>
+      <c r="C103" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Сосенское</t>
+        </is>
+      </c>
+      <c r="D103" s="36" t="inlineStr">
+        <is>
+          <t>77-002949</t>
+        </is>
+      </c>
+      <c r="E103" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/55224</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
@@ -10731,12 +11823,24 @@
           <t>55472</t>
         </is>
       </c>
-      <c r="B104" s="27" t="n"/>
-      <c r="C104" s="27" t="n"/>
-      <c r="D104" s="27" t="n"/>
-      <c r="E104" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Родные кварталы</t>
+        </is>
+      </c>
+      <c r="C104" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Марушкинское</t>
+        </is>
+      </c>
+      <c r="D104" s="27" t="inlineStr">
+        <is>
+          <t>77-002959</t>
+        </is>
+      </c>
+      <c r="E104" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/55472</t>
         </is>
       </c>
       <c r="F104" s="26" t="inlineStr">
@@ -10821,12 +11925,24 @@
           <t>55760</t>
         </is>
       </c>
-      <c r="B105" s="36" t="n"/>
-      <c r="C105" s="36" t="n"/>
-      <c r="D105" s="36" t="n"/>
-      <c r="E105" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B105" s="36" t="inlineStr">
+        <is>
+          <t>Квартал Домашний,ЖК Квартал Домашний</t>
+        </is>
+      </c>
+      <c r="C105" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Марьино</t>
+        </is>
+      </c>
+      <c r="D105" s="36" t="inlineStr">
+        <is>
+          <t>77-002964</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/55760</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
@@ -10912,12 +12028,24 @@
           <t>56071</t>
         </is>
       </c>
-      <c r="B106" s="27" t="n"/>
-      <c r="C106" s="27" t="n"/>
-      <c r="D106" s="27" t="n"/>
-      <c r="E106" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>Молжаниново, ЖК Молжаниново</t>
+        </is>
+      </c>
+      <c r="C106" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Молжаниновский район</t>
+        </is>
+      </c>
+      <c r="D106" s="27" t="inlineStr">
+        <is>
+          <t>77-002968</t>
+        </is>
+      </c>
+      <c r="E106" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56071</t>
         </is>
       </c>
       <c r="F106" s="26" t="inlineStr">
@@ -11003,12 +12131,24 @@
           <t>56102</t>
         </is>
       </c>
-      <c r="B107" s="36" t="n"/>
-      <c r="C107" s="36" t="n"/>
-      <c r="D107" s="36" t="n"/>
-      <c r="E107" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B107" s="36" t="inlineStr">
+        <is>
+          <t>КУРКИНО15</t>
+        </is>
+      </c>
+      <c r="C107" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Куркино, шоссе Куркинское, вл. 15</t>
+        </is>
+      </c>
+      <c r="D107" s="36" t="inlineStr">
+        <is>
+          <t>77-002969</t>
+        </is>
+      </c>
+      <c r="E107" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56102</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
@@ -11093,12 +12233,24 @@
           <t>56157</t>
         </is>
       </c>
-      <c r="B108" s="27" t="n"/>
-      <c r="C108" s="27" t="n"/>
-      <c r="D108" s="27" t="n"/>
-      <c r="E108" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>ЖК 1-й Ясеневский</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Коммунарка</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="inlineStr">
+        <is>
+          <t>77-002970</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56157</t>
         </is>
       </c>
       <c r="F108" s="26" t="inlineStr">
@@ -11183,12 +12335,24 @@
           <t>56224</t>
         </is>
       </c>
-      <c r="B109" s="36" t="n"/>
-      <c r="C109" s="36" t="n"/>
-      <c r="D109" s="36" t="n"/>
-      <c r="E109" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B109" s="36" t="inlineStr">
+        <is>
+          <t>Clos 17/ Кло 17</t>
+        </is>
+      </c>
+      <c r="C109" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Арбат</t>
+        </is>
+      </c>
+      <c r="D109" s="36" t="inlineStr">
+        <is>
+          <t>77-002973</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56224</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
@@ -11273,12 +12437,24 @@
           <t>56304</t>
         </is>
       </c>
-      <c r="B110" s="27" t="n"/>
-      <c r="C110" s="27" t="n"/>
-      <c r="D110" s="27" t="n"/>
-      <c r="E110" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Остафьево,ПРАГМАТИК-КЛАСС</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Щербинка</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="inlineStr">
+        <is>
+          <t>77-002977</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56304</t>
         </is>
       </c>
       <c r="F110" s="26" t="inlineStr">
@@ -11363,12 +12539,24 @@
           <t>56305</t>
         </is>
       </c>
-      <c r="B111" s="36" t="n"/>
-      <c r="C111" s="36" t="n"/>
-      <c r="D111" s="36" t="n"/>
-      <c r="E111" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B111" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Остафьево,ПРАГМАТИК-КЛАСС</t>
+        </is>
+      </c>
+      <c r="C111" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Щербинка</t>
+        </is>
+      </c>
+      <c r="D111" s="36" t="inlineStr">
+        <is>
+          <t>77-002977</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56305</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
@@ -11453,12 +12641,24 @@
           <t>56306</t>
         </is>
       </c>
-      <c r="B112" s="27" t="n"/>
-      <c r="C112" s="27" t="n"/>
-      <c r="D112" s="27" t="n"/>
-      <c r="E112" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Остафьево,ПРАГМАТИК-КЛАСС</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Рязановское</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>77-002978</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56306</t>
         </is>
       </c>
       <c r="F112" s="26" t="inlineStr">
@@ -11543,12 +12743,24 @@
           <t>56307</t>
         </is>
       </c>
-      <c r="B113" s="36" t="n"/>
-      <c r="C113" s="36" t="n"/>
-      <c r="D113" s="36" t="n"/>
-      <c r="E113" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B113" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Остафьево,ПРАГМАТИК-КЛАСС</t>
+        </is>
+      </c>
+      <c r="C113" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Рязановское</t>
+        </is>
+      </c>
+      <c r="D113" s="36" t="inlineStr">
+        <is>
+          <t>77-002978</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56307</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
@@ -11633,12 +12845,24 @@
           <t>56514</t>
         </is>
       </c>
-      <c r="B114" s="27" t="n"/>
-      <c r="C114" s="27" t="n"/>
-      <c r="D114" s="27" t="n"/>
-      <c r="E114" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>ЖК 1-й Ясеневский</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Коммунарка</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>77-002986</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56514</t>
         </is>
       </c>
       <c r="F114" s="26" t="inlineStr">
@@ -11724,12 +12948,24 @@
           <t>45970</t>
         </is>
       </c>
-      <c r="B115" s="36" t="n"/>
-      <c r="C115" s="36" t="n"/>
-      <c r="D115" s="36" t="n"/>
-      <c r="E115" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B115" s="36" t="inlineStr">
+        <is>
+          <t>Ривер Парк Кутузовский</t>
+        </is>
+      </c>
+      <c r="C115" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Дорогомилово</t>
+        </is>
+      </c>
+      <c r="D115" s="36" t="inlineStr">
+        <is>
+          <t>77-002477</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/45970</t>
         </is>
       </c>
       <c r="F115" s="35" t="inlineStr">
@@ -11811,12 +13047,24 @@
           <t>56715</t>
         </is>
       </c>
-      <c r="B116" s="27" t="n"/>
-      <c r="C116" s="27" t="n"/>
-      <c r="D116" s="27" t="n"/>
-      <c r="E116" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>Квартал Марьино, ЖК Квартал Марьино</t>
+        </is>
+      </c>
+      <c r="C116" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Филимонковский</t>
+        </is>
+      </c>
+      <c r="D116" s="27" t="inlineStr">
+        <is>
+          <t>77-002991</t>
+        </is>
+      </c>
+      <c r="E116" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56715</t>
         </is>
       </c>
       <c r="F116" s="26" t="inlineStr">
@@ -11902,12 +13150,24 @@
           <t>56866</t>
         </is>
       </c>
-      <c r="B117" s="36" t="n"/>
-      <c r="C117" s="36" t="n"/>
-      <c r="D117" s="36" t="n"/>
-      <c r="E117" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B117" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Эко Бунино, Жилой комплекс Эко Бунино</t>
+        </is>
+      </c>
+      <c r="C117" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Коммунарка</t>
+        </is>
+      </c>
+      <c r="D117" s="36" t="inlineStr">
+        <is>
+          <t>77-002996</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56866</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
@@ -11992,12 +13252,24 @@
           <t>56944</t>
         </is>
       </c>
-      <c r="B118" s="27" t="n"/>
-      <c r="C118" s="27" t="n"/>
-      <c r="D118" s="27" t="n"/>
-      <c r="E118" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Новое Внуково</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Кокошкино</t>
+        </is>
+      </c>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>77-002998</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56944</t>
         </is>
       </c>
       <c r="F118" s="26" t="inlineStr">
@@ -12083,12 +13355,24 @@
           <t>56945</t>
         </is>
       </c>
-      <c r="B119" s="36" t="n"/>
-      <c r="C119" s="36" t="n"/>
-      <c r="D119" s="36" t="n"/>
-      <c r="E119" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B119" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Новое Внуково</t>
+        </is>
+      </c>
+      <c r="C119" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Кокошкино</t>
+        </is>
+      </c>
+      <c r="D119" s="36" t="inlineStr">
+        <is>
+          <t>77-002998</t>
+        </is>
+      </c>
+      <c r="E119" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56945</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
@@ -12174,12 +13458,24 @@
           <t>56949</t>
         </is>
       </c>
-      <c r="B120" s="27" t="n"/>
-      <c r="C120" s="27" t="n"/>
-      <c r="D120" s="27" t="n"/>
-      <c r="E120" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>ЖК "Новое Внуково"</t>
+        </is>
+      </c>
+      <c r="C120" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Кокошкино</t>
+        </is>
+      </c>
+      <c r="D120" s="27" t="inlineStr">
+        <is>
+          <t>77-002999</t>
+        </is>
+      </c>
+      <c r="E120" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56949</t>
         </is>
       </c>
       <c r="F120" s="26" t="inlineStr">
@@ -12265,12 +13561,24 @@
           <t>56950</t>
         </is>
       </c>
-      <c r="B121" s="36" t="n"/>
-      <c r="C121" s="36" t="n"/>
-      <c r="D121" s="36" t="n"/>
-      <c r="E121" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B121" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Новое Внуково"</t>
+        </is>
+      </c>
+      <c r="C121" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Кокошкино</t>
+        </is>
+      </c>
+      <c r="D121" s="36" t="inlineStr">
+        <is>
+          <t>77-002999</t>
+        </is>
+      </c>
+      <c r="E121" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/56950</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
@@ -12355,12 +13663,24 @@
           <t>57478</t>
         </is>
       </c>
-      <c r="B122" s="27" t="n"/>
-      <c r="C122" s="27" t="n"/>
-      <c r="D122" s="27" t="n"/>
-      <c r="E122" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Западный квартал, Западный квартал</t>
+        </is>
+      </c>
+      <c r="C122" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Марушкинское</t>
+        </is>
+      </c>
+      <c r="D122" s="27" t="inlineStr">
+        <is>
+          <t>77-003012</t>
+        </is>
+      </c>
+      <c r="E122" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/57478</t>
         </is>
       </c>
       <c r="F122" s="26" t="inlineStr">
@@ -12446,12 +13766,24 @@
           <t>58298</t>
         </is>
       </c>
-      <c r="B123" s="36" t="n"/>
-      <c r="C123" s="36" t="n"/>
-      <c r="D123" s="36" t="n"/>
-      <c r="E123" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B123" s="36" t="inlineStr">
+        <is>
+          <t>ЖК Западный квартал, Западный квартал</t>
+        </is>
+      </c>
+      <c r="C123" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Марушкинское</t>
+        </is>
+      </c>
+      <c r="D123" s="36" t="inlineStr">
+        <is>
+          <t>77-003034</t>
+        </is>
+      </c>
+      <c r="E123" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/58298</t>
         </is>
       </c>
       <c r="F123" s="35" t="inlineStr">
@@ -12537,12 +13869,24 @@
           <t>58299</t>
         </is>
       </c>
-      <c r="B124" s="27" t="n"/>
-      <c r="C124" s="27" t="n"/>
-      <c r="D124" s="27" t="n"/>
-      <c r="E124" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Западный квартал, Западный квартал</t>
+        </is>
+      </c>
+      <c r="C124" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Марушкинское</t>
+        </is>
+      </c>
+      <c r="D124" s="27" t="inlineStr">
+        <is>
+          <t>77-003034</t>
+        </is>
+      </c>
+      <c r="E124" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/58299</t>
         </is>
       </c>
       <c r="F124" s="26" t="inlineStr">
@@ -12628,12 +13972,24 @@
           <t>58524</t>
         </is>
       </c>
-      <c r="B125" s="36" t="n"/>
-      <c r="C125" s="36" t="n"/>
-      <c r="D125" s="36" t="n"/>
-      <c r="E125" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B125" s="36" t="inlineStr">
+        <is>
+          <t>АРТЕЛЬ</t>
+        </is>
+      </c>
+      <c r="C125" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Преображенское</t>
+        </is>
+      </c>
+      <c r="D125" s="36" t="inlineStr">
+        <is>
+          <t>77-003041</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/58524</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
@@ -12718,12 +14074,24 @@
           <t>59897</t>
         </is>
       </c>
-      <c r="B126" s="27" t="n"/>
-      <c r="C126" s="27" t="n"/>
-      <c r="D126" s="27" t="n"/>
-      <c r="E126" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>ЖК"Южные сады"</t>
+        </is>
+      </c>
+      <c r="C126" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Южное Бутово</t>
+        </is>
+      </c>
+      <c r="D126" s="27" t="inlineStr">
+        <is>
+          <t>77-003067</t>
+        </is>
+      </c>
+      <c r="E126" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/59897</t>
         </is>
       </c>
       <c r="F126" s="26" t="inlineStr">
@@ -12809,12 +14177,24 @@
           <t>60712</t>
         </is>
       </c>
-      <c r="B127" s="36" t="n"/>
-      <c r="C127" s="36" t="n"/>
-      <c r="D127" s="36" t="n"/>
-      <c r="E127" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B127" s="36" t="inlineStr">
+        <is>
+          <t>Дом Горизонтов</t>
+        </is>
+      </c>
+      <c r="C127" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Крылатское</t>
+        </is>
+      </c>
+      <c r="D127" s="36" t="inlineStr">
+        <is>
+          <t>77-003080</t>
+        </is>
+      </c>
+      <c r="E127" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/60712</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
@@ -12900,12 +14280,24 @@
           <t>61221</t>
         </is>
       </c>
-      <c r="B128" s="27" t="n"/>
-      <c r="C128" s="27" t="n"/>
-      <c r="D128" s="27" t="n"/>
-      <c r="E128" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B128" s="27" t="inlineStr">
+        <is>
+          <t>Жилой комплекс Кронштадтский 9</t>
+        </is>
+      </c>
+      <c r="C128" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Головинский район</t>
+        </is>
+      </c>
+      <c r="D128" s="27" t="inlineStr">
+        <is>
+          <t>77-003088</t>
+        </is>
+      </c>
+      <c r="E128" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/61221</t>
         </is>
       </c>
       <c r="F128" s="26" t="inlineStr">
@@ -12991,12 +14383,24 @@
           <t>50365</t>
         </is>
       </c>
-      <c r="B129" s="36" t="n"/>
-      <c r="C129" s="36" t="n"/>
-      <c r="D129" s="36" t="n"/>
-      <c r="E129" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B129" s="36" t="inlineStr">
+        <is>
+          <t>Селигер Сити</t>
+        </is>
+      </c>
+      <c r="C129" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, ш Дмитровское, вл. 87, блок-секция Блок -секция Корпус G</t>
+        </is>
+      </c>
+      <c r="D129" s="36" t="inlineStr">
+        <is>
+          <t>77-002820</t>
+        </is>
+      </c>
+      <c r="E129" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/50365</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
@@ -13078,12 +14482,24 @@
           <t>51432</t>
         </is>
       </c>
-      <c r="B130" s="27" t="n"/>
-      <c r="C130" s="27" t="n"/>
-      <c r="D130" s="27" t="n"/>
-      <c r="E130" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B130" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Дом Дау</t>
+        </is>
+      </c>
+      <c r="C130" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Пресненский район</t>
+        </is>
+      </c>
+      <c r="D130" s="27" t="inlineStr">
+        <is>
+          <t>77-002845</t>
+        </is>
+      </c>
+      <c r="E130" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/51432</t>
         </is>
       </c>
       <c r="F130" s="26" t="inlineStr">
@@ -13164,12 +14580,24 @@
           <t>54528</t>
         </is>
       </c>
-      <c r="B131" s="36" t="n"/>
-      <c r="C131" s="36" t="n"/>
-      <c r="D131" s="36" t="n"/>
-      <c r="E131" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B131" s="36" t="inlineStr">
+        <is>
+          <t>Жилой комплекс "Кутузовский квартал"</t>
+        </is>
+      </c>
+      <c r="C131" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Кунцево</t>
+        </is>
+      </c>
+      <c r="D131" s="36" t="inlineStr">
+        <is>
+          <t>77-002928</t>
+        </is>
+      </c>
+      <c r="E131" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/54528</t>
         </is>
       </c>
       <c r="F131" s="35" t="inlineStr">
@@ -13251,12 +14679,24 @@
           <t>55103</t>
         </is>
       </c>
-      <c r="B132" s="27" t="n"/>
-      <c r="C132" s="27" t="n"/>
-      <c r="D132" s="27" t="n"/>
-      <c r="E132" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B132" s="27" t="inlineStr">
+        <is>
+          <t>Николь, Николь Клуб и Николь Резиденция</t>
+        </is>
+      </c>
+      <c r="C132" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, г. Москва, район Тверской р-н, ул Никольская, д. 10/2, литера АВ, строение 2</t>
+        </is>
+      </c>
+      <c r="D132" s="27" t="inlineStr">
+        <is>
+          <t>77-002943</t>
+        </is>
+      </c>
+      <c r="E132" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/55103</t>
         </is>
       </c>
       <c r="F132" s="26" t="inlineStr">
@@ -13338,12 +14778,24 @@
           <t>57291</t>
         </is>
       </c>
-      <c r="B133" s="36" t="n"/>
-      <c r="C133" s="36" t="n"/>
-      <c r="D133" s="36" t="n"/>
-      <c r="E133" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B133" s="36" t="inlineStr">
+        <is>
+          <t>Жилой комплекс "Бусиновский парк"</t>
+        </is>
+      </c>
+      <c r="C133" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Западное Дегунино</t>
+        </is>
+      </c>
+      <c r="D133" s="36" t="inlineStr">
+        <is>
+          <t>77-003008</t>
+        </is>
+      </c>
+      <c r="E133" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/57291</t>
         </is>
       </c>
       <c r="F133" s="35" t="inlineStr">
@@ -13425,12 +14877,24 @@
           <t>57465</t>
         </is>
       </c>
-      <c r="B134" s="27" t="n"/>
-      <c r="C134" s="27" t="n"/>
-      <c r="D134" s="27" t="n"/>
-      <c r="E134" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B134" s="27" t="inlineStr">
+        <is>
+          <t>ЖК "КИНГ &amp; САНС"</t>
+        </is>
+      </c>
+      <c r="C134" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Раменки</t>
+        </is>
+      </c>
+      <c r="D134" s="27" t="inlineStr">
+        <is>
+          <t>77-003011</t>
+        </is>
+      </c>
+      <c r="E134" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/57465</t>
         </is>
       </c>
       <c r="F134" s="26" t="inlineStr">
@@ -13512,12 +14976,24 @@
           <t>57807</t>
         </is>
       </c>
-      <c r="B135" s="36" t="n"/>
-      <c r="C135" s="36" t="n"/>
-      <c r="D135" s="36" t="n"/>
-      <c r="E135" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B135" s="36" t="inlineStr">
+        <is>
+          <t>Преображенская площадь. Жилой комплекс</t>
+        </is>
+      </c>
+      <c r="C135" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Преображенское</t>
+        </is>
+      </c>
+      <c r="D135" s="36" t="inlineStr">
+        <is>
+          <t>77-003014</t>
+        </is>
+      </c>
+      <c r="E135" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/57807</t>
         </is>
       </c>
       <c r="F135" s="35" t="inlineStr">
@@ -13599,12 +15075,24 @@
           <t>58300</t>
         </is>
       </c>
-      <c r="B136" s="27" t="n"/>
-      <c r="C136" s="27" t="n"/>
-      <c r="D136" s="27" t="n"/>
-      <c r="E136" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B136" s="27" t="inlineStr">
+        <is>
+          <t>ГОРОД МОСКВА, Район Дорогомилово</t>
+        </is>
+      </c>
+      <c r="C136" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Дорогомилово</t>
+        </is>
+      </c>
+      <c r="D136" s="27" t="inlineStr">
+        <is>
+          <t>77-003035</t>
+        </is>
+      </c>
+      <c r="E136" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/58300</t>
         </is>
       </c>
       <c r="F136" s="26" t="inlineStr">
@@ -13686,12 +15174,24 @@
           <t>58488</t>
         </is>
       </c>
-      <c r="B137" s="36" t="n"/>
-      <c r="C137" s="36" t="n"/>
-      <c r="D137" s="36" t="n"/>
-      <c r="E137" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B137" s="36" t="inlineStr">
+        <is>
+          <t>Тишинский бульвар</t>
+        </is>
+      </c>
+      <c r="C137" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Пресненский район</t>
+        </is>
+      </c>
+      <c r="D137" s="36" t="inlineStr">
+        <is>
+          <t>77-003039</t>
+        </is>
+      </c>
+      <c r="E137" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/58488</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
@@ -13772,12 +15272,24 @@
           <t>58489</t>
         </is>
       </c>
-      <c r="B138" s="27" t="n"/>
-      <c r="C138" s="27" t="n"/>
-      <c r="D138" s="27" t="n"/>
-      <c r="E138" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B138" s="27" t="inlineStr">
+        <is>
+          <t>Тишинский бульвар</t>
+        </is>
+      </c>
+      <c r="C138" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Пресненский район</t>
+        </is>
+      </c>
+      <c r="D138" s="27" t="inlineStr">
+        <is>
+          <t>77-003040</t>
+        </is>
+      </c>
+      <c r="E138" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/58489</t>
         </is>
       </c>
       <c r="F138" s="26" t="inlineStr">
@@ -13858,12 +15370,24 @@
           <t>60425</t>
         </is>
       </c>
-      <c r="B139" s="36" t="n"/>
-      <c r="C139" s="36" t="n"/>
-      <c r="D139" s="36" t="n"/>
-      <c r="E139" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B139" s="36" t="inlineStr">
+        <is>
+          <t>ХАЙДАУТ</t>
+        </is>
+      </c>
+      <c r="C139" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Раменки</t>
+        </is>
+      </c>
+      <c r="D139" s="36" t="inlineStr">
+        <is>
+          <t>77-003073</t>
+        </is>
+      </c>
+      <c r="E139" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/60425</t>
         </is>
       </c>
       <c r="F139" s="35" t="inlineStr">
@@ -13946,12 +15470,24 @@
           <t>62125</t>
         </is>
       </c>
-      <c r="B140" s="27" t="n"/>
-      <c r="C140" s="27" t="n"/>
-      <c r="D140" s="27" t="n"/>
-      <c r="E140" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B140" s="27" t="inlineStr">
+        <is>
+          <t>ЖК Эра ЖК Премиум-квартал Эра</t>
+        </is>
+      </c>
+      <c r="C140" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Даниловский район</t>
+        </is>
+      </c>
+      <c r="D140" s="27" t="inlineStr">
+        <is>
+          <t>77-003115</t>
+        </is>
+      </c>
+      <c r="E140" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/62125</t>
         </is>
       </c>
       <c r="F140" s="26" t="inlineStr">
@@ -14032,12 +15568,24 @@
           <t>62998</t>
         </is>
       </c>
-      <c r="B141" s="36" t="n"/>
-      <c r="C141" s="36" t="n"/>
-      <c r="D141" s="36" t="n"/>
-      <c r="E141" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B141" s="36" t="inlineStr">
+        <is>
+          <t>МИРА</t>
+        </is>
+      </c>
+      <c r="C141" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Алексеевский район</t>
+        </is>
+      </c>
+      <c r="D141" s="36" t="inlineStr">
+        <is>
+          <t>77-003131</t>
+        </is>
+      </c>
+      <c r="E141" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/62998</t>
         </is>
       </c>
       <c r="F141" s="35" t="inlineStr">
@@ -14122,12 +15670,24 @@
           <t>63646</t>
         </is>
       </c>
-      <c r="B142" s="27" t="n"/>
-      <c r="C142" s="27" t="n"/>
-      <c r="D142" s="27" t="n"/>
-      <c r="E142" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B142" s="27" t="inlineStr">
+        <is>
+          <t>Жилой комплекс "1-й Измайловский"</t>
+        </is>
+      </c>
+      <c r="C142" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Гольяново</t>
+        </is>
+      </c>
+      <c r="D142" s="27" t="inlineStr">
+        <is>
+          <t>77-003145</t>
+        </is>
+      </c>
+      <c r="E142" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/63646</t>
         </is>
       </c>
       <c r="F142" s="26" t="inlineStr">
@@ -14213,12 +15773,24 @@
           <t>65505</t>
         </is>
       </c>
-      <c r="B143" s="36" t="n"/>
-      <c r="C143" s="36" t="n"/>
-      <c r="D143" s="36" t="n"/>
-      <c r="E143" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B143" s="36" t="inlineStr">
+        <is>
+          <t>ЖК "Троицкий"</t>
+        </is>
+      </c>
+      <c r="C143" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, район Поселение Троицк</t>
+        </is>
+      </c>
+      <c r="D143" s="36" t="inlineStr">
+        <is>
+          <t>77-003189</t>
+        </is>
+      </c>
+      <c r="E143" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/65505</t>
         </is>
       </c>
       <c r="F143" s="35" t="inlineStr">
@@ -14303,12 +15875,24 @@
           <t>66242</t>
         </is>
       </c>
-      <c r="B144" s="27" t="n"/>
-      <c r="C144" s="27" t="n"/>
-      <c r="D144" s="27" t="n"/>
-      <c r="E144" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B144" s="27" t="inlineStr">
+        <is>
+          <t>Верейская 41</t>
+        </is>
+      </c>
+      <c r="C144" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Можайский район</t>
+        </is>
+      </c>
+      <c r="D144" s="27" t="inlineStr">
+        <is>
+          <t>77-002429</t>
+        </is>
+      </c>
+      <c r="E144" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/66242</t>
         </is>
       </c>
       <c r="F144" s="26" t="inlineStr">
@@ -14394,12 +15978,24 @@
           <t>67699</t>
         </is>
       </c>
-      <c r="B145" s="36" t="n"/>
-      <c r="C145" s="36" t="n"/>
-      <c r="D145" s="36" t="n"/>
-      <c r="E145" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B145" s="36" t="inlineStr">
+        <is>
+          <t>Жилой квартал PRIME PARK</t>
+        </is>
+      </c>
+      <c r="C145" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Хорошёвский район</t>
+        </is>
+      </c>
+      <c r="D145" s="36" t="inlineStr">
+        <is>
+          <t>77-003244</t>
+        </is>
+      </c>
+      <c r="E145" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/67699</t>
         </is>
       </c>
       <c r="F145" s="35" t="inlineStr">
@@ -14484,12 +16080,24 @@
           <t>67700</t>
         </is>
       </c>
-      <c r="B146" s="27" t="n"/>
-      <c r="C146" s="27" t="n"/>
-      <c r="D146" s="27" t="n"/>
-      <c r="E146" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B146" s="27" t="inlineStr">
+        <is>
+          <t>Жилой квартал PRIME PARK</t>
+        </is>
+      </c>
+      <c r="C146" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Хорошёвский район</t>
+        </is>
+      </c>
+      <c r="D146" s="27" t="inlineStr">
+        <is>
+          <t>77-003244</t>
+        </is>
+      </c>
+      <c r="E146" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/67700</t>
         </is>
       </c>
       <c r="F146" s="26" t="inlineStr">
@@ -14574,12 +16182,24 @@
           <t>69273</t>
         </is>
       </c>
-      <c r="B147" s="36" t="n"/>
-      <c r="C147" s="36" t="n"/>
-      <c r="D147" s="36" t="n"/>
-      <c r="E147" s="36" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B147" s="36" t="inlineStr">
+        <is>
+          <t>Сити Бэй</t>
+        </is>
+      </c>
+      <c r="C147" s="36" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Район Покровское-Стрешнево</t>
+        </is>
+      </c>
+      <c r="D147" s="36" t="inlineStr">
+        <is>
+          <t>77-002343</t>
+        </is>
+      </c>
+      <c r="E147" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/69273</t>
         </is>
       </c>
       <c r="F147" s="35" t="inlineStr">
@@ -14664,12 +16284,24 @@
           <t>70718</t>
         </is>
       </c>
-      <c r="B148" s="27" t="n"/>
-      <c r="C148" s="27" t="n"/>
-      <c r="D148" s="27" t="n"/>
-      <c r="E148" s="27" t="inlineStr">
-        <is>
-          <t>не заполнено: дом.рф повторно выдал антибот; требуется проверка источника</t>
+      <c r="B148" s="27" t="inlineStr">
+        <is>
+          <t>ЖК «Первый Рязанский»</t>
+        </is>
+      </c>
+      <c r="C148" s="27" t="inlineStr">
+        <is>
+          <t>Москва город, ГОРОД МОСКВА, Рязанский район</t>
+        </is>
+      </c>
+      <c r="D148" s="27" t="inlineStr">
+        <is>
+          <t>77-003305</t>
+        </is>
+      </c>
+      <c r="E148" s="28" t="inlineStr">
+        <is>
+          <t>https://xn--80az8a.xn--d1aqf.xn--p1ai/%D1%81%D0%B5%D1%80%D0%B2%D0%B8%D1%81%D1%8B/%D0%BA%D0%B0%D1%82%D0%B0%D0%BB%D0%BE%D0%B3-%D0%BD%D0%BE%D0%B2%D0%BE%D1%81%D1%82%D1%80%D0%BE%D0%B5%D0%BA/%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82/70718</t>
         </is>
       </c>
       <c r="F148" s="26" t="inlineStr">
@@ -14757,11 +16389,147 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.7000000476837158" right="0.7000000476837158" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
